--- a/assets/modelo_ponderacao.xlsx
+++ b/assets/modelo_ponderacao.xlsx
@@ -1008,7 +1008,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R41"/>
+  <dimension ref="B1:R41"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.88671875" defaultRowHeight="13.2"/>
   <cols>
     <col width="4.33203125" customWidth="1" style="31" min="1" max="1"/>
@@ -1123,7 +1123,6 @@
       <c r="Q9" s="20" t="n"/>
       <c r="R9" s="21" t="n"/>
     </row>
-    <row r="10"/>
     <row r="11" ht="18" customHeight="1" s="37" thickBot="1">
       <c r="B11" s="35" t="n"/>
       <c r="K11" s="35" t="n"/>
@@ -1225,7 +1224,6 @@
       <c r="Q17" s="20" t="n"/>
       <c r="R17" s="21" t="n"/>
     </row>
-    <row r="18"/>
     <row r="19" ht="18" customHeight="1" s="37" thickBot="1">
       <c r="B19" s="35" t="n"/>
       <c r="K19" s="35" t="n"/>
@@ -1572,12 +1570,6 @@
     <mergeCell ref="M11:R11"/>
     <mergeCell ref="B11:G11"/>
   </mergeCells>
-  <conditionalFormatting sqref="K7:K8 K13:K16 K21:K24">
-    <cfRule type="cellIs" priority="3" operator="notBetween" dxfId="2" stopIfTrue="1">
-      <formula>2</formula>
-      <formula>-2</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.787401575" bottom="0.787401575" header="0.31496062" footer="0.31496062"/>
   <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
